--- a/Setting up your lab/Data Files/UserSecurity.xlsx
+++ b/Setting up your lab/Data Files/UserSecurity.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64af166a96f05eac/Business Intelligence/Courses/AI^J Claude^J Power BI Course/Data Files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB8E21C3-BB4A-479B-9CBE-018B45637DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139DABC3-DCD5-4297-9E74-C52A5D71F0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{410C5EFB-E3F1-46A4-93AD-A8CACAFE978B}"/>
   </bookViews>
@@ -569,8 +564,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>